--- a/data/branch_weight_data.xlsx
+++ b/data/branch_weight_data.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\McGrath\occ-coseismic\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Frontiers abroad\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E188C29-ADD1-42B2-9D1C-FE56D6AAB92C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0694C0B-4A28-4DB3-9219-23FE48700F8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="827" uniqueCount="296">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="819" uniqueCount="292">
   <si>
     <t>N</t>
   </si>
@@ -864,70 +864,58 @@
     <t>ti</t>
   </si>
   <si>
-    <t>sz_solutions/FakeQuakes_hk_3e10_nolocking_uniformSlip_n5000_S10_N1_GR500_b1-1_N21-5_nIt500000_narchi10</t>
-  </si>
-  <si>
-    <t>sz_solutions/FakeQuakes_hk_prem_nolocking_uniformSlip_n5000_S10_N1_GR500_b1-1_N21-5_nIt500000_narchi10</t>
-  </si>
-  <si>
-    <t>sz_solutions/FakeQuakes_hk_prem_nolocking_n5000_S10_N1_GR500_b1-1_N21-5_nIt500000_narchi10</t>
-  </si>
-  <si>
-    <t>sz_solutions/FakeQuakes_hk_3e10_locking_n5000_S10_N1_GR500_b1-1_N21-5_nIt500000_narchi10</t>
-  </si>
-  <si>
-    <t>sz_solutions/FakeQuakes_hk_prem_locking_n5000_S10_N1_GR500_b1-1_N21-5_nIt500000_narchi10</t>
-  </si>
-  <si>
-    <t>sz_solutions/FakeQuakes_hk_3e10_nolocking_n5000_S10_N1_GR500_b1-1_N21-5_nIt500000_narchi10</t>
-  </si>
-  <si>
-    <t>_sz_fq_3nub110</t>
-  </si>
-  <si>
-    <t>_sz_fq_pnub110</t>
-  </si>
-  <si>
-    <t>_sz_fq_3nhb110</t>
-  </si>
-  <si>
-    <t>_sz_fq_pnhb110</t>
-  </si>
-  <si>
-    <t>_sz_fq_3lhb110</t>
-  </si>
-  <si>
-    <t>_sz_fq_plhb110</t>
-  </si>
-  <si>
-    <t>sz_solutions/FakeQuakes_hk_3e10_locking_n5000_S1_N1_GR500_b1-1_N21-5_nIt500000_narchi10</t>
-  </si>
-  <si>
-    <t>sz_solutions/FakeQuakes_hk_3e10_locking_n5000_S100_N1_GR500_b1-1_N21-5_nIt500000_narchi10</t>
-  </si>
-  <si>
-    <t>_sz_fq_3lhb110C100</t>
-  </si>
-  <si>
-    <t>_sz_fq_3lhb110C1</t>
-  </si>
-  <si>
-    <t>_sz_fq_3nhb110C1</t>
-  </si>
-  <si>
-    <t>sz_solutions/FakeQuakes_hk_3e10_nolocking_n5000_S1_N1_GR500_b1-1_N21-5_nIt500000_narchi10</t>
-  </si>
-  <si>
-    <t>sz_solutions/FakeQuakes_hk_3e10_nolocking_n5000_S100_N1_GR500_b1-1_N21-5_nIt500000_narchi10</t>
-  </si>
-  <si>
-    <t>sz_solutions/FakeQuakes_hk_3e10_locking_n5000_S1000_N1_GR500_b1-1_N21-5_nIt500000_narchi10</t>
-  </si>
-  <si>
-    <t>_sz_fq_3lhb110C1000</t>
-  </si>
-  <si>
-    <t>_sz_fq_3nhb110C100</t>
+    <t>sz_solutions/FrontiersAbroad_hk_trenchcreep_v_SDlock_locking_n5000_S10_N1_GR500_b1-1_N21-5_nIt500000_narchi2</t>
+  </si>
+  <si>
+    <t>sz_solutions/FrontiersAbroad_hk_trenchcreep_v_SDcreep_locking_n5000_S10_N1_GR500_b1-1_N21-5_nIt500000_narchi2</t>
+  </si>
+  <si>
+    <t>sz_solutions/FrontiersAbroad_hk_trenchcreep_v_SDplate70_locking_n5000_S10_N1_GR500_b1-1_N21-5_nIt500000_narchi2</t>
+  </si>
+  <si>
+    <t>sz_solutions/FrontiersAbroad_hk_trenchlock_v_SDlock_locking_n5000_S10_N1_GR500_b1-1_N21-5_nIt500000_narchi2</t>
+  </si>
+  <si>
+    <t>sz_solutions/FrontiersAbroad_hk_trenchlock_v_SDcreep_locking_n5000_S10_N1_GR500_b1-1_N21-5_nIt500000_narchi2</t>
+  </si>
+  <si>
+    <t>sz_solutions/FrontiersAbroad_hk_trenchlock_v_SDplate70_locking_n5000_S10_N1_GR500_b1-1_N21-5_nIt500000_narchi2</t>
+  </si>
+  <si>
+    <t>sz_solutions/FrontiersAbroad_hk_plate70_v_SDlock_locking_n5000_S10_N1_GR500_b1-1_N21-5_nIt500000_narchi2</t>
+  </si>
+  <si>
+    <t>sz_solutions/FrontiersAbroad_hk_plate70_v_SDcreep_locking_n5000_S10_N1_GR500_b1-1_N21-5_nIt500000_narchi2</t>
+  </si>
+  <si>
+    <t>sz_solutions/FrontiersAbroad_hk_plate70_v_SDplate70_locking_n5000_S10_N1_GR500_b1-1_N21-5_nIt500000_narchi2</t>
+  </si>
+  <si>
+    <t>_sz_fq_FA_tc_l</t>
+  </si>
+  <si>
+    <t>_sz_fq_FA_tc_c</t>
+  </si>
+  <si>
+    <t>_sz_fq_FA_tc_p70</t>
+  </si>
+  <si>
+    <t>_sz_fq_FA_tl_l</t>
+  </si>
+  <si>
+    <t>_sz_fq_FA_tl_c</t>
+  </si>
+  <si>
+    <t>_sz_fq_FA_tl_p70</t>
+  </si>
+  <si>
+    <t>_sz_fq_FA_p70_l</t>
+  </si>
+  <si>
+    <t>_sz_fq_FA_p70_c</t>
+  </si>
+  <si>
+    <t>_sz_fq_FA_p70_p70</t>
   </si>
 </sst>
 </file>
@@ -7280,7 +7268,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{97C3AB27-DA22-46B6-9275-CBA251195A6D}">
-  <dimension ref="A1:P12"/>
+  <dimension ref="A1:P10"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.7109375" customWidth="1"/>
@@ -7371,18 +7359,18 @@
         <v>0.22018730999999997</v>
       </c>
       <c r="J2">
-        <v>1.2753645444283894E-4</v>
+        <v>1.27536454442839E-4</v>
       </c>
       <c r="K2">
         <f t="shared" ref="K2" si="1">J2*I2</f>
-        <v>2.8081908830706253E-5</v>
+        <v>2.8081908830706263E-5</v>
       </c>
       <c r="L2">
-        <f t="shared" ref="L2:L9" si="2">K2/(SUM(K$2:K$42))</f>
-        <v>9.0909090909090939E-2</v>
+        <f>K2/(SUM(K$2:K$18))</f>
+        <v>0.11111111111111112</v>
       </c>
       <c r="M2" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="N2" t="s">
         <v>274</v>
@@ -7414,22 +7402,22 @@
         <v>0.48699999999999999</v>
       </c>
       <c r="I3">
-        <f t="shared" ref="I3" si="3">PRODUCT(G3:H3)</f>
+        <f t="shared" ref="I3:I10" si="2">PRODUCT(G3:H3)</f>
         <v>0.22018730999999997</v>
       </c>
       <c r="J3">
-        <v>1.2753645444283894E-4</v>
+        <v>1.27536454442839E-4</v>
       </c>
       <c r="K3">
-        <f t="shared" ref="K3" si="4">J3*I3</f>
-        <v>2.8081908830706253E-5</v>
+        <f t="shared" ref="K3:K10" si="3">J3*I3</f>
+        <v>2.8081908830706263E-5</v>
       </c>
       <c r="L3">
-        <f t="shared" si="2"/>
-        <v>9.0909090909090939E-2</v>
+        <f>K3/(SUM(K$2:K$18))</f>
+        <v>0.11111111111111112</v>
       </c>
       <c r="M3" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="N3" t="s">
         <v>275</v>
@@ -7461,25 +7449,25 @@
         <v>0.48699999999999999</v>
       </c>
       <c r="I4">
-        <f t="shared" ref="I4:I6" si="5">PRODUCT(G4:H4)</f>
+        <f t="shared" si="2"/>
         <v>0.22018730999999997</v>
       </c>
       <c r="J4">
-        <v>1.2753645444283894E-4</v>
+        <v>1.27536454442839E-4</v>
       </c>
       <c r="K4">
-        <f t="shared" ref="K4:K6" si="6">J4*I4</f>
-        <v>2.8081908830706253E-5</v>
+        <f t="shared" si="3"/>
+        <v>2.8081908830706263E-5</v>
       </c>
       <c r="L4">
-        <f t="shared" si="2"/>
-        <v>9.0909090909090939E-2</v>
+        <f>K4/(SUM(K$2:K$18))</f>
+        <v>0.11111111111111112</v>
       </c>
       <c r="M4" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="N4" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.25">
@@ -7508,25 +7496,25 @@
         <v>0.48699999999999999</v>
       </c>
       <c r="I5">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>0.22018730999999997</v>
       </c>
       <c r="J5">
-        <v>1.2753645444283894E-4</v>
+        <v>1.27536454442839E-4</v>
       </c>
       <c r="K5">
-        <f t="shared" si="6"/>
-        <v>2.8081908830706253E-5</v>
+        <f t="shared" si="3"/>
+        <v>2.8081908830706263E-5</v>
       </c>
       <c r="L5">
-        <f t="shared" si="2"/>
-        <v>9.0909090909090939E-2</v>
+        <f>K5/(SUM(K$2:K$18))</f>
+        <v>0.11111111111111112</v>
       </c>
       <c r="M5" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="N5" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.25">
@@ -7555,25 +7543,25 @@
         <v>0.48699999999999999</v>
       </c>
       <c r="I6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>0.22018730999999997</v>
       </c>
       <c r="J6">
-        <v>1.2753645444283894E-4</v>
+        <v>1.27536454442839E-4</v>
       </c>
       <c r="K6">
-        <f t="shared" si="6"/>
-        <v>2.8081908830706253E-5</v>
+        <f t="shared" si="3"/>
+        <v>2.8081908830706263E-5</v>
       </c>
       <c r="L6">
-        <f t="shared" si="2"/>
-        <v>9.0909090909090939E-2</v>
+        <f>K6/(SUM(K$2:K$18))</f>
+        <v>0.11111111111111112</v>
       </c>
       <c r="M6" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="N6" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.25">
@@ -7602,25 +7590,25 @@
         <v>0.48699999999999999</v>
       </c>
       <c r="I7">
-        <f t="shared" ref="I7:I11" si="7">PRODUCT(G7:H7)</f>
+        <f t="shared" si="2"/>
         <v>0.22018730999999997</v>
       </c>
       <c r="J7">
-        <v>1.2753645444283894E-4</v>
+        <v>1.27536454442839E-4</v>
       </c>
       <c r="K7">
-        <f t="shared" ref="K7:K11" si="8">J7*I7</f>
-        <v>2.8081908830706253E-5</v>
+        <f t="shared" si="3"/>
+        <v>2.8081908830706263E-5</v>
       </c>
       <c r="L7">
-        <f t="shared" si="2"/>
-        <v>9.0909090909090939E-2</v>
+        <f>K7/(SUM(K$2:K$18))</f>
+        <v>0.11111111111111112</v>
       </c>
       <c r="M7" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="N7" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.25">
@@ -7649,25 +7637,25 @@
         <v>0.48699999999999999</v>
       </c>
       <c r="I8">
-        <f t="shared" si="7"/>
+        <f t="shared" si="2"/>
         <v>0.22018730999999997</v>
       </c>
       <c r="J8">
-        <v>1.2753645444283894E-4</v>
+        <v>1.27536454442839E-4</v>
       </c>
       <c r="K8">
-        <f t="shared" si="8"/>
-        <v>2.8081908830706253E-5</v>
+        <f t="shared" si="3"/>
+        <v>2.8081908830706263E-5</v>
       </c>
       <c r="L8">
-        <f t="shared" si="2"/>
-        <v>9.0909090909090939E-2</v>
+        <f>K8/(SUM(K$2:K$18))</f>
+        <v>0.11111111111111112</v>
       </c>
       <c r="M8" t="s">
         <v>289</v>
       </c>
       <c r="N8" t="s">
-        <v>286</v>
+        <v>280</v>
       </c>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.25">
@@ -7696,25 +7684,25 @@
         <v>0.48699999999999999</v>
       </c>
       <c r="I9">
-        <f t="shared" si="7"/>
+        <f t="shared" si="2"/>
         <v>0.22018730999999997</v>
       </c>
       <c r="J9">
-        <v>1.2753645444283894E-4</v>
+        <v>1.27536454442839E-4</v>
       </c>
       <c r="K9">
-        <f t="shared" si="8"/>
-        <v>2.8081908830706253E-5</v>
+        <f t="shared" si="3"/>
+        <v>2.8081908830706263E-5</v>
       </c>
       <c r="L9">
-        <f t="shared" si="2"/>
-        <v>9.0909090909090939E-2</v>
+        <f>K9/(SUM(K$2:K$18))</f>
+        <v>0.11111111111111112</v>
       </c>
       <c r="M9" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="N9" t="s">
-        <v>287</v>
+        <v>281</v>
       </c>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.25">
@@ -7743,124 +7731,31 @@
         <v>0.48699999999999999</v>
       </c>
       <c r="I10">
-        <f t="shared" ref="I10" si="9">PRODUCT(G10:H10)</f>
+        <f t="shared" si="2"/>
         <v>0.22018730999999997</v>
       </c>
       <c r="J10">
-        <v>1.2753645444283894E-4</v>
+        <v>1.27536454442839E-4</v>
       </c>
       <c r="K10">
-        <f t="shared" ref="K10" si="10">J10*I10</f>
-        <v>2.8081908830706253E-5</v>
+        <f t="shared" si="3"/>
+        <v>2.8081908830706263E-5</v>
       </c>
       <c r="L10">
-        <f t="shared" ref="L10" si="11">K10/(SUM(K$2:K$42))</f>
-        <v>9.0909090909090939E-2</v>
+        <f>K10/(SUM(K$2:K$18))</f>
+        <v>0.11111111111111112</v>
       </c>
       <c r="M10" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="N10" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A11">
-        <v>21.5</v>
-      </c>
-      <c r="B11">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="C11">
-        <v>4</v>
-      </c>
-      <c r="D11">
-        <v>1</v>
-      </c>
-      <c r="E11" t="s">
-        <v>257</v>
-      </c>
-      <c r="F11" t="s">
-        <v>260</v>
-      </c>
-      <c r="G11">
-        <v>0.45212999999999998</v>
-      </c>
-      <c r="H11">
-        <v>0.48699999999999999</v>
-      </c>
-      <c r="I11">
-        <f t="shared" si="7"/>
-        <v>0.22018730999999997</v>
-      </c>
-      <c r="J11">
-        <v>1.2753645444283894E-4</v>
-      </c>
-      <c r="K11">
-        <f t="shared" si="8"/>
-        <v>2.8081908830706253E-5</v>
-      </c>
-      <c r="L11">
-        <f t="shared" ref="L11:L12" si="12">K11/(SUM(K$2:K$42))</f>
-        <v>9.0909090909090939E-2</v>
-      </c>
-      <c r="M11" t="s">
-        <v>290</v>
-      </c>
-      <c r="N11" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A12">
-        <v>21.5</v>
-      </c>
-      <c r="B12">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="C12">
-        <v>4</v>
-      </c>
-      <c r="D12">
-        <v>1</v>
-      </c>
-      <c r="E12" t="s">
-        <v>257</v>
-      </c>
-      <c r="F12" t="s">
-        <v>260</v>
-      </c>
-      <c r="G12">
-        <v>0.45212999999999998</v>
-      </c>
-      <c r="H12">
-        <v>0.48699999999999999</v>
-      </c>
-      <c r="I12">
-        <f t="shared" ref="I12" si="13">PRODUCT(G12:H12)</f>
-        <v>0.22018730999999997</v>
-      </c>
-      <c r="J12">
-        <v>1.2753645444283894E-4</v>
-      </c>
-      <c r="K12">
-        <f t="shared" ref="K12" si="14">J12*I12</f>
-        <v>2.8081908830706253E-5</v>
-      </c>
-      <c r="L12">
-        <f t="shared" si="12"/>
-        <v>9.0909090909090939E-2</v>
-      </c>
-      <c r="M12" t="s">
-        <v>295</v>
-      </c>
-      <c r="N12" t="s">
-        <v>292</v>
+        <v>282</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="20" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <headerFooter>
     <oddFooter>&amp;C_x000D_&amp;1#&amp;"Calibri"&amp;7&amp;K000000 Classification: In-Confidence</oddFooter>
   </headerFooter>

--- a/data/branch_weight_data.xlsx
+++ b/data/branch_weight_data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Frontiers abroad\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jdmcg\Documents\POSTAL\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0694C0B-4A28-4DB3-9219-23FE48700F8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FAC8E4E-9301-40CC-9039-3F367F34E902}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="11625" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="all sheets" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="819" uniqueCount="292">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="795" uniqueCount="280">
   <si>
     <t>N</t>
   </si>
@@ -864,55 +864,19 @@
     <t>ti</t>
   </si>
   <si>
-    <t>sz_solutions/FrontiersAbroad_hk_trenchcreep_v_SDlock_locking_n5000_S10_N1_GR500_b1-1_N21-5_nIt500000_narchi2</t>
-  </si>
-  <si>
     <t>sz_solutions/FrontiersAbroad_hk_trenchcreep_v_SDcreep_locking_n5000_S10_N1_GR500_b1-1_N21-5_nIt500000_narchi2</t>
   </si>
   <si>
-    <t>sz_solutions/FrontiersAbroad_hk_trenchcreep_v_SDplate70_locking_n5000_S10_N1_GR500_b1-1_N21-5_nIt500000_narchi2</t>
-  </si>
-  <si>
     <t>sz_solutions/FrontiersAbroad_hk_trenchlock_v_SDlock_locking_n5000_S10_N1_GR500_b1-1_N21-5_nIt500000_narchi2</t>
   </si>
   <si>
-    <t>sz_solutions/FrontiersAbroad_hk_trenchlock_v_SDcreep_locking_n5000_S10_N1_GR500_b1-1_N21-5_nIt500000_narchi2</t>
-  </si>
-  <si>
-    <t>sz_solutions/FrontiersAbroad_hk_trenchlock_v_SDplate70_locking_n5000_S10_N1_GR500_b1-1_N21-5_nIt500000_narchi2</t>
-  </si>
-  <si>
-    <t>sz_solutions/FrontiersAbroad_hk_plate70_v_SDlock_locking_n5000_S10_N1_GR500_b1-1_N21-5_nIt500000_narchi2</t>
-  </si>
-  <si>
-    <t>sz_solutions/FrontiersAbroad_hk_plate70_v_SDcreep_locking_n5000_S10_N1_GR500_b1-1_N21-5_nIt500000_narchi2</t>
-  </si>
-  <si>
     <t>sz_solutions/FrontiersAbroad_hk_plate70_v_SDplate70_locking_n5000_S10_N1_GR500_b1-1_N21-5_nIt500000_narchi2</t>
   </si>
   <si>
-    <t>_sz_fq_FA_tc_l</t>
-  </si>
-  <si>
     <t>_sz_fq_FA_tc_c</t>
   </si>
   <si>
-    <t>_sz_fq_FA_tc_p70</t>
-  </si>
-  <si>
     <t>_sz_fq_FA_tl_l</t>
-  </si>
-  <si>
-    <t>_sz_fq_FA_tl_c</t>
-  </si>
-  <si>
-    <t>_sz_fq_FA_tl_p70</t>
-  </si>
-  <si>
-    <t>_sz_fq_FA_p70_l</t>
-  </si>
-  <si>
-    <t>_sz_fq_FA_p70_c</t>
   </si>
   <si>
     <t>_sz_fq_FA_p70_p70</t>
@@ -1797,13 +1761,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G59"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="4" max="4" width="41.7109375" customWidth="1"/>
-    <col min="5" max="5" width="8.28515625" customWidth="1"/>
+    <col min="4" max="4" width="41.73046875" customWidth="1"/>
+    <col min="5" max="5" width="8.265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1823,7 +1787,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A2">
         <v>27.9</v>
       </c>
@@ -1843,7 +1807,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A3">
         <v>21.5</v>
       </c>
@@ -1863,7 +1827,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A4">
         <v>27.9</v>
       </c>
@@ -1883,7 +1847,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A5">
         <v>21.5</v>
       </c>
@@ -1903,7 +1867,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A6">
         <v>27.9</v>
       </c>
@@ -1923,7 +1887,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A7">
         <v>21.5</v>
       </c>
@@ -1943,7 +1907,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A8">
         <v>16.5</v>
       </c>
@@ -1963,7 +1927,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A9">
         <v>27.9</v>
       </c>
@@ -1983,7 +1947,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A10">
         <v>16.5</v>
       </c>
@@ -2003,7 +1967,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A11">
         <v>27.9</v>
       </c>
@@ -2023,7 +1987,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A12">
         <v>16.5</v>
       </c>
@@ -2043,7 +2007,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A13">
         <v>27.9</v>
       </c>
@@ -2063,7 +2027,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A14">
         <v>21.5</v>
       </c>
@@ -2083,7 +2047,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A15">
         <v>16.5</v>
       </c>
@@ -2103,7 +2067,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A16">
         <v>21.5</v>
       </c>
@@ -2123,7 +2087,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A17">
         <v>16.5</v>
       </c>
@@ -2143,7 +2107,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A18">
         <v>21.5</v>
       </c>
@@ -2163,7 +2127,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A19">
         <v>16.5</v>
       </c>
@@ -2183,7 +2147,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A21">
         <v>4.5999999999999996</v>
       </c>
@@ -2203,7 +2167,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A22">
         <v>4.5999999999999996</v>
       </c>
@@ -2223,7 +2187,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A23">
         <v>2.7</v>
       </c>
@@ -2243,7 +2207,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A24">
         <v>4.5999999999999996</v>
       </c>
@@ -2263,7 +2227,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A25">
         <v>3.4</v>
       </c>
@@ -2283,7 +2247,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A26">
         <v>3.4</v>
       </c>
@@ -2303,7 +2267,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A27">
         <v>2.7</v>
       </c>
@@ -2323,7 +2287,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A28">
         <v>3.4</v>
       </c>
@@ -2343,7 +2307,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A29">
         <v>2.7</v>
       </c>
@@ -2363,7 +2327,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A31">
         <v>4.5999999999999996</v>
       </c>
@@ -2383,7 +2347,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A32">
         <v>3.4</v>
       </c>
@@ -2403,7 +2367,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A33">
         <v>4.5999999999999996</v>
       </c>
@@ -2423,7 +2387,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A34">
         <v>2.7</v>
       </c>
@@ -2443,7 +2407,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A35">
         <v>4.5999999999999996</v>
       </c>
@@ -2463,7 +2427,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A36">
         <v>2.7</v>
       </c>
@@ -2483,7 +2447,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A37">
         <v>2.7</v>
       </c>
@@ -2503,7 +2467,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A38">
         <v>3.4</v>
       </c>
@@ -2523,7 +2487,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A39">
         <v>3.4</v>
       </c>
@@ -2543,7 +2507,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A41">
         <v>4.5999999999999996</v>
       </c>
@@ -2563,7 +2527,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A42">
         <v>4.5999999999999996</v>
       </c>
@@ -2583,7 +2547,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A43">
         <v>2.7</v>
       </c>
@@ -2603,7 +2567,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A44">
         <v>4.5999999999999996</v>
       </c>
@@ -2623,7 +2587,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A45">
         <v>3.4</v>
       </c>
@@ -2643,7 +2607,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A46">
         <v>3.4</v>
       </c>
@@ -2663,7 +2627,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A47">
         <v>2.7</v>
       </c>
@@ -2683,7 +2647,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A48">
         <v>3.4</v>
       </c>
@@ -2703,7 +2667,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A49">
         <v>2.7</v>
       </c>
@@ -2723,7 +2687,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A51">
         <v>4.5999999999999996</v>
       </c>
@@ -2743,7 +2707,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A52">
         <v>3.4</v>
       </c>
@@ -2763,7 +2727,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A53">
         <v>4.5999999999999996</v>
       </c>
@@ -2783,7 +2747,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A54">
         <v>2.7</v>
       </c>
@@ -2803,7 +2767,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A55">
         <v>4.5999999999999996</v>
       </c>
@@ -2823,7 +2787,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A56">
         <v>2.7</v>
       </c>
@@ -2843,7 +2807,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A57">
         <v>2.7</v>
       </c>
@@ -2863,7 +2827,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A58">
         <v>3.4</v>
       </c>
@@ -2883,7 +2847,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A59">
         <v>3.4</v>
       </c>
@@ -2914,15 +2878,15 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:L41"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="5" max="7" width="20" customWidth="1"/>
-    <col min="8" max="9" width="16.42578125" customWidth="1"/>
-    <col min="10" max="10" width="53.7109375" customWidth="1"/>
-    <col min="11" max="11" width="73.140625" customWidth="1"/>
+    <col min="8" max="9" width="16.3984375" customWidth="1"/>
+    <col min="10" max="10" width="53.73046875" customWidth="1"/>
+    <col min="11" max="11" width="73.1328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2960,7 +2924,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A2" s="1">
         <v>4.5999999999999996</v>
       </c>
@@ -2995,7 +2959,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="3" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A3" s="2">
         <v>3.4</v>
       </c>
@@ -3030,7 +2994,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="4" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A4" s="1">
         <v>2.7</v>
       </c>
@@ -3065,7 +3029,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A6">
         <v>4.5999999999999996</v>
       </c>
@@ -3100,7 +3064,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A7">
         <v>2.7</v>
       </c>
@@ -3135,7 +3099,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A8">
         <v>4.5999999999999996</v>
       </c>
@@ -3170,7 +3134,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A9">
         <v>3.4</v>
       </c>
@@ -3205,7 +3169,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A10">
         <v>3.4</v>
       </c>
@@ -3240,7 +3204,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A11">
         <v>2.7</v>
       </c>
@@ -3275,7 +3239,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A13">
         <v>4.5999999999999996</v>
       </c>
@@ -3310,7 +3274,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A14">
         <v>3.4</v>
       </c>
@@ -3345,7 +3309,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A15">
         <v>4.5999999999999996</v>
       </c>
@@ -3380,7 +3344,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A16">
         <v>2.7</v>
       </c>
@@ -3415,7 +3379,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A17">
         <v>4.5999999999999996</v>
       </c>
@@ -3450,7 +3414,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A18">
         <v>2.7</v>
       </c>
@@ -3485,7 +3449,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A19">
         <v>2.7</v>
       </c>
@@ -3520,7 +3484,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A20">
         <v>3.4</v>
       </c>
@@ -3555,7 +3519,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A21">
         <v>3.4</v>
       </c>
@@ -3590,7 +3554,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A23">
         <v>4.5999999999999996</v>
       </c>
@@ -3625,7 +3589,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A24">
         <v>4.5999999999999996</v>
       </c>
@@ -3660,7 +3624,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A25">
         <v>2.7</v>
       </c>
@@ -3695,7 +3659,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A26">
         <v>4.5999999999999996</v>
       </c>
@@ -3730,7 +3694,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A27">
         <v>3.4</v>
       </c>
@@ -3765,7 +3729,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A28">
         <v>3.4</v>
       </c>
@@ -3800,7 +3764,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A29">
         <v>2.7</v>
       </c>
@@ -3835,7 +3799,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A30">
         <v>3.4</v>
       </c>
@@ -3870,7 +3834,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A31">
         <v>2.7</v>
       </c>
@@ -3905,7 +3869,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A33">
         <v>4.5999999999999996</v>
       </c>
@@ -3940,7 +3904,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A34">
         <v>3.4</v>
       </c>
@@ -3975,7 +3939,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A35">
         <v>4.5999999999999996</v>
       </c>
@@ -4010,7 +3974,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A36">
         <v>2.7</v>
       </c>
@@ -4045,7 +4009,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A37">
         <v>4.5999999999999996</v>
       </c>
@@ -4080,7 +4044,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A38">
         <v>2.7</v>
       </c>
@@ -4115,7 +4079,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A39">
         <v>2.7</v>
       </c>
@@ -4150,7 +4114,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A40">
         <v>3.4</v>
       </c>
@@ -4185,7 +4149,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A41">
         <v>3.4</v>
       </c>
@@ -4232,20 +4196,20 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{05C99C73-6827-4669-8FE0-2897EFBDB8B0}">
   <dimension ref="A1:R37"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="6.85546875" customWidth="1"/>
-    <col min="2" max="2" width="6.42578125" customWidth="1"/>
-    <col min="3" max="3" width="6.140625" customWidth="1"/>
-    <col min="5" max="5" width="11.42578125" customWidth="1"/>
-    <col min="6" max="6" width="21.28515625" customWidth="1"/>
-    <col min="14" max="14" width="16.42578125" customWidth="1"/>
-    <col min="15" max="15" width="19.42578125" customWidth="1"/>
-    <col min="16" max="16" width="14.5703125" customWidth="1"/>
-    <col min="17" max="17" width="26.140625" customWidth="1"/>
+    <col min="1" max="1" width="6.86328125" customWidth="1"/>
+    <col min="2" max="2" width="6.3984375" customWidth="1"/>
+    <col min="3" max="3" width="6.1328125" customWidth="1"/>
+    <col min="5" max="5" width="11.3984375" customWidth="1"/>
+    <col min="6" max="6" width="21.265625" customWidth="1"/>
+    <col min="14" max="14" width="16.3984375" customWidth="1"/>
+    <col min="15" max="15" width="19.3984375" customWidth="1"/>
+    <col min="16" max="16" width="14.59765625" customWidth="1"/>
+    <col min="17" max="17" width="26.1328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -4301,7 +4265,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A2">
         <v>2.7</v>
       </c>
@@ -4360,7 +4324,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A3">
         <v>2.7</v>
       </c>
@@ -4410,7 +4374,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A4">
         <v>2.7</v>
       </c>
@@ -4460,7 +4424,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A5">
         <v>3.4</v>
       </c>
@@ -4519,7 +4483,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A6">
         <v>3.4</v>
       </c>
@@ -4569,7 +4533,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A7">
         <v>3.4</v>
       </c>
@@ -4619,7 +4583,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A8">
         <v>4.5999999999999996</v>
       </c>
@@ -4678,7 +4642,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A9">
         <v>4.5999999999999996</v>
       </c>
@@ -4728,7 +4692,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A10">
         <v>4.5999999999999996</v>
       </c>
@@ -4778,7 +4742,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A11">
         <v>2.7</v>
       </c>
@@ -4837,7 +4801,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A12">
         <v>2.7</v>
       </c>
@@ -4887,7 +4851,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A13">
         <v>2.7</v>
       </c>
@@ -4937,7 +4901,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A14">
         <v>3.4</v>
       </c>
@@ -4996,7 +4960,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A15">
         <v>3.4</v>
       </c>
@@ -5046,7 +5010,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A16">
         <v>3.4</v>
       </c>
@@ -5096,7 +5060,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="17" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A17">
         <v>4.5999999999999996</v>
       </c>
@@ -5155,7 +5119,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="18" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A18">
         <v>4.5999999999999996</v>
       </c>
@@ -5205,7 +5169,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="19" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A19">
         <v>4.5999999999999996</v>
       </c>
@@ -5255,7 +5219,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="20" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A20">
         <v>2.7</v>
       </c>
@@ -5314,7 +5278,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="21" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A21">
         <v>2.7</v>
       </c>
@@ -5364,7 +5328,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="22" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A22">
         <v>2.7</v>
       </c>
@@ -5414,7 +5378,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="23" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A23">
         <v>3.4</v>
       </c>
@@ -5473,7 +5437,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="24" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A24">
         <v>3.4</v>
       </c>
@@ -5523,7 +5487,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="25" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A25">
         <v>3.4</v>
       </c>
@@ -5573,7 +5537,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="26" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A26">
         <v>4.5999999999999996</v>
       </c>
@@ -5632,7 +5596,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="27" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A27">
         <v>4.5999999999999996</v>
       </c>
@@ -5682,7 +5646,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="28" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A28">
         <v>4.5999999999999996</v>
       </c>
@@ -5732,7 +5696,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="29" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A29">
         <v>2.7</v>
       </c>
@@ -5791,7 +5755,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="30" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A30">
         <v>2.7</v>
       </c>
@@ -5841,7 +5805,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="31" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A31">
         <v>2.7</v>
       </c>
@@ -5891,7 +5855,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="32" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A32">
         <v>3.4</v>
       </c>
@@ -5950,7 +5914,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="33" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A33">
         <v>3.4</v>
       </c>
@@ -6000,7 +5964,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="34" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A34">
         <v>3.4</v>
       </c>
@@ -6050,7 +6014,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="35" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A35">
         <v>4.5999999999999996</v>
       </c>
@@ -6109,7 +6073,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="36" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A36">
         <v>4.5999999999999996</v>
       </c>
@@ -6159,7 +6123,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="37" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A37">
         <v>4.5999999999999996</v>
       </c>
@@ -6221,15 +6185,15 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:I20"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="11.7109375" customWidth="1"/>
-    <col min="5" max="6" width="38.5703125" customWidth="1"/>
-    <col min="7" max="7" width="85.42578125" customWidth="1"/>
-    <col min="8" max="8" width="52.140625" customWidth="1"/>
+    <col min="1" max="1" width="11.73046875" customWidth="1"/>
+    <col min="5" max="6" width="38.59765625" customWidth="1"/>
+    <col min="7" max="7" width="85.3984375" customWidth="1"/>
+    <col min="8" max="8" width="52.1328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -6258,7 +6222,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A2" s="1">
         <v>27.9</v>
       </c>
@@ -6287,7 +6251,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="3" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A3" s="2">
         <v>21.5</v>
       </c>
@@ -6316,7 +6280,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="4" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A4" s="1">
         <v>16.5</v>
       </c>
@@ -6345,7 +6309,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A6">
         <v>27.9</v>
       </c>
@@ -6374,7 +6338,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A7">
         <v>21.5</v>
       </c>
@@ -6403,7 +6367,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A8">
         <v>16.5</v>
       </c>
@@ -6432,7 +6396,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A9">
         <v>27.9</v>
       </c>
@@ -6461,7 +6425,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A10">
         <v>21.5</v>
       </c>
@@ -6490,7 +6454,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A11">
         <v>27.9</v>
       </c>
@@ -6519,7 +6483,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A12">
         <v>21.5</v>
       </c>
@@ -6548,7 +6512,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A13">
         <v>16.5</v>
       </c>
@@ -6577,7 +6541,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A14">
         <v>27.9</v>
       </c>
@@ -6606,7 +6570,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A15">
         <v>16.5</v>
       </c>
@@ -6635,7 +6599,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A16">
         <v>27.9</v>
       </c>
@@ -6664,7 +6628,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A17">
         <v>21.5</v>
       </c>
@@ -6693,7 +6657,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A18">
         <v>16.5</v>
       </c>
@@ -6722,7 +6686,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A19">
         <v>21.5</v>
       </c>
@@ -6751,7 +6715,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A20">
         <v>16.5</v>
       </c>
@@ -6792,17 +6756,17 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B44185B4-3219-47A6-B13D-018C1909CFFA}">
   <dimension ref="A1:P10"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="11.7109375" customWidth="1"/>
-    <col min="5" max="10" width="12.5703125" customWidth="1"/>
-    <col min="11" max="11" width="15.28515625" customWidth="1"/>
-    <col min="12" max="12" width="15.140625" customWidth="1"/>
-    <col min="13" max="13" width="35.5703125" customWidth="1"/>
-    <col min="14" max="14" width="10.42578125" customWidth="1"/>
+    <col min="1" max="1" width="11.73046875" customWidth="1"/>
+    <col min="5" max="10" width="12.59765625" customWidth="1"/>
+    <col min="11" max="11" width="15.265625" customWidth="1"/>
+    <col min="12" max="12" width="15.1328125" customWidth="1"/>
+    <col min="13" max="13" width="35.59765625" customWidth="1"/>
+    <col min="14" max="14" width="10.3984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -6852,7 +6816,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A2">
         <v>27.9</v>
       </c>
@@ -6899,7 +6863,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A3">
         <v>27.9</v>
       </c>
@@ -6943,7 +6907,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A4">
         <v>27.9</v>
       </c>
@@ -6987,7 +6951,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A5">
         <v>21.5</v>
       </c>
@@ -7034,7 +6998,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A6">
         <v>21.5</v>
       </c>
@@ -7078,7 +7042,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A7">
         <v>21.5</v>
       </c>
@@ -7122,7 +7086,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A8">
         <v>16.5</v>
       </c>
@@ -7169,7 +7133,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A9">
         <v>16.5</v>
       </c>
@@ -7213,7 +7177,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A10">
         <v>16.5</v>
       </c>
@@ -7268,18 +7232,18 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{97C3AB27-DA22-46B6-9275-CBA251195A6D}">
-  <dimension ref="A1:P10"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:P4"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="11.7109375" customWidth="1"/>
-    <col min="5" max="10" width="12.5703125" customWidth="1"/>
-    <col min="11" max="11" width="15.28515625" customWidth="1"/>
-    <col min="12" max="12" width="15.140625" customWidth="1"/>
-    <col min="13" max="13" width="35.5703125" customWidth="1"/>
-    <col min="14" max="14" width="10.42578125" customWidth="1"/>
+    <col min="1" max="1" width="11.73046875" customWidth="1"/>
+    <col min="5" max="10" width="12.59765625" customWidth="1"/>
+    <col min="11" max="11" width="15.265625" customWidth="1"/>
+    <col min="12" max="12" width="15.1328125" customWidth="1"/>
+    <col min="13" max="13" width="35.59765625" customWidth="1"/>
+    <col min="14" max="14" width="10.3984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -7329,7 +7293,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A2">
         <v>21.5</v>
       </c>
@@ -7355,28 +7319,28 @@
         <v>0.48699999999999999</v>
       </c>
       <c r="I2">
-        <f t="shared" ref="I2" si="0">PRODUCT(G2:H2)</f>
+        <f t="shared" ref="I2:I4" si="0">PRODUCT(G2:H2)</f>
         <v>0.22018730999999997</v>
       </c>
       <c r="J2">
         <v>1.27536454442839E-4</v>
       </c>
       <c r="K2">
-        <f t="shared" ref="K2" si="1">J2*I2</f>
+        <f t="shared" ref="K2:K4" si="1">J2*I2</f>
         <v>2.8081908830706263E-5</v>
       </c>
       <c r="L2">
-        <f>K2/(SUM(K$2:K$18))</f>
-        <v>0.11111111111111112</v>
+        <f>K2/(SUM(K$2:K$12))</f>
+        <v>0.33333333333333337</v>
       </c>
       <c r="M2" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="N2" t="s">
         <v>274</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A3">
         <v>21.5</v>
       </c>
@@ -7402,28 +7366,28 @@
         <v>0.48699999999999999</v>
       </c>
       <c r="I3">
-        <f t="shared" ref="I3:I10" si="2">PRODUCT(G3:H3)</f>
+        <f t="shared" si="0"/>
         <v>0.22018730999999997</v>
       </c>
       <c r="J3">
         <v>1.27536454442839E-4</v>
       </c>
       <c r="K3">
-        <f t="shared" ref="K3:K10" si="3">J3*I3</f>
+        <f t="shared" si="1"/>
         <v>2.8081908830706263E-5</v>
       </c>
       <c r="L3">
-        <f>K3/(SUM(K$2:K$18))</f>
-        <v>0.11111111111111112</v>
+        <f>K3/(SUM(K$2:K$12))</f>
+        <v>0.33333333333333337</v>
       </c>
       <c r="M3" t="s">
-        <v>284</v>
+        <v>278</v>
       </c>
       <c r="N3" t="s">
         <v>275</v>
       </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A4">
         <v>21.5</v>
       </c>
@@ -7449,307 +7413,25 @@
         <v>0.48699999999999999</v>
       </c>
       <c r="I4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0.22018730999999997</v>
       </c>
       <c r="J4">
         <v>1.27536454442839E-4</v>
       </c>
       <c r="K4">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>2.8081908830706263E-5</v>
       </c>
       <c r="L4">
-        <f>K4/(SUM(K$2:K$18))</f>
-        <v>0.11111111111111112</v>
+        <f>K4/(SUM(K$2:K$12))</f>
+        <v>0.33333333333333337</v>
       </c>
       <c r="M4" t="s">
-        <v>285</v>
+        <v>279</v>
       </c>
       <c r="N4" t="s">
         <v>276</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A5">
-        <v>21.5</v>
-      </c>
-      <c r="B5">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="C5">
-        <v>4</v>
-      </c>
-      <c r="D5">
-        <v>1</v>
-      </c>
-      <c r="E5" t="s">
-        <v>257</v>
-      </c>
-      <c r="F5" t="s">
-        <v>260</v>
-      </c>
-      <c r="G5">
-        <v>0.45212999999999998</v>
-      </c>
-      <c r="H5">
-        <v>0.48699999999999999</v>
-      </c>
-      <c r="I5">
-        <f t="shared" si="2"/>
-        <v>0.22018730999999997</v>
-      </c>
-      <c r="J5">
-        <v>1.27536454442839E-4</v>
-      </c>
-      <c r="K5">
-        <f t="shared" si="3"/>
-        <v>2.8081908830706263E-5</v>
-      </c>
-      <c r="L5">
-        <f>K5/(SUM(K$2:K$18))</f>
-        <v>0.11111111111111112</v>
-      </c>
-      <c r="M5" t="s">
-        <v>286</v>
-      </c>
-      <c r="N5" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A6">
-        <v>21.5</v>
-      </c>
-      <c r="B6">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="C6">
-        <v>4</v>
-      </c>
-      <c r="D6">
-        <v>1</v>
-      </c>
-      <c r="E6" t="s">
-        <v>257</v>
-      </c>
-      <c r="F6" t="s">
-        <v>260</v>
-      </c>
-      <c r="G6">
-        <v>0.45212999999999998</v>
-      </c>
-      <c r="H6">
-        <v>0.48699999999999999</v>
-      </c>
-      <c r="I6">
-        <f t="shared" si="2"/>
-        <v>0.22018730999999997</v>
-      </c>
-      <c r="J6">
-        <v>1.27536454442839E-4</v>
-      </c>
-      <c r="K6">
-        <f t="shared" si="3"/>
-        <v>2.8081908830706263E-5</v>
-      </c>
-      <c r="L6">
-        <f>K6/(SUM(K$2:K$18))</f>
-        <v>0.11111111111111112</v>
-      </c>
-      <c r="M6" t="s">
-        <v>287</v>
-      </c>
-      <c r="N6" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A7">
-        <v>21.5</v>
-      </c>
-      <c r="B7">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="C7">
-        <v>4</v>
-      </c>
-      <c r="D7">
-        <v>1</v>
-      </c>
-      <c r="E7" t="s">
-        <v>257</v>
-      </c>
-      <c r="F7" t="s">
-        <v>260</v>
-      </c>
-      <c r="G7">
-        <v>0.45212999999999998</v>
-      </c>
-      <c r="H7">
-        <v>0.48699999999999999</v>
-      </c>
-      <c r="I7">
-        <f t="shared" si="2"/>
-        <v>0.22018730999999997</v>
-      </c>
-      <c r="J7">
-        <v>1.27536454442839E-4</v>
-      </c>
-      <c r="K7">
-        <f t="shared" si="3"/>
-        <v>2.8081908830706263E-5</v>
-      </c>
-      <c r="L7">
-        <f>K7/(SUM(K$2:K$18))</f>
-        <v>0.11111111111111112</v>
-      </c>
-      <c r="M7" t="s">
-        <v>288</v>
-      </c>
-      <c r="N7" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A8">
-        <v>21.5</v>
-      </c>
-      <c r="B8">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="C8">
-        <v>4</v>
-      </c>
-      <c r="D8">
-        <v>1</v>
-      </c>
-      <c r="E8" t="s">
-        <v>257</v>
-      </c>
-      <c r="F8" t="s">
-        <v>260</v>
-      </c>
-      <c r="G8">
-        <v>0.45212999999999998</v>
-      </c>
-      <c r="H8">
-        <v>0.48699999999999999</v>
-      </c>
-      <c r="I8">
-        <f t="shared" si="2"/>
-        <v>0.22018730999999997</v>
-      </c>
-      <c r="J8">
-        <v>1.27536454442839E-4</v>
-      </c>
-      <c r="K8">
-        <f t="shared" si="3"/>
-        <v>2.8081908830706263E-5</v>
-      </c>
-      <c r="L8">
-        <f>K8/(SUM(K$2:K$18))</f>
-        <v>0.11111111111111112</v>
-      </c>
-      <c r="M8" t="s">
-        <v>289</v>
-      </c>
-      <c r="N8" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A9">
-        <v>21.5</v>
-      </c>
-      <c r="B9">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="C9">
-        <v>4</v>
-      </c>
-      <c r="D9">
-        <v>1</v>
-      </c>
-      <c r="E9" t="s">
-        <v>257</v>
-      </c>
-      <c r="F9" t="s">
-        <v>260</v>
-      </c>
-      <c r="G9">
-        <v>0.45212999999999998</v>
-      </c>
-      <c r="H9">
-        <v>0.48699999999999999</v>
-      </c>
-      <c r="I9">
-        <f t="shared" si="2"/>
-        <v>0.22018730999999997</v>
-      </c>
-      <c r="J9">
-        <v>1.27536454442839E-4</v>
-      </c>
-      <c r="K9">
-        <f t="shared" si="3"/>
-        <v>2.8081908830706263E-5</v>
-      </c>
-      <c r="L9">
-        <f>K9/(SUM(K$2:K$18))</f>
-        <v>0.11111111111111112</v>
-      </c>
-      <c r="M9" t="s">
-        <v>290</v>
-      </c>
-      <c r="N9" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A10">
-        <v>21.5</v>
-      </c>
-      <c r="B10">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="C10">
-        <v>4</v>
-      </c>
-      <c r="D10">
-        <v>1</v>
-      </c>
-      <c r="E10" t="s">
-        <v>257</v>
-      </c>
-      <c r="F10" t="s">
-        <v>260</v>
-      </c>
-      <c r="G10">
-        <v>0.45212999999999998</v>
-      </c>
-      <c r="H10">
-        <v>0.48699999999999999</v>
-      </c>
-      <c r="I10">
-        <f t="shared" si="2"/>
-        <v>0.22018730999999997</v>
-      </c>
-      <c r="J10">
-        <v>1.27536454442839E-4</v>
-      </c>
-      <c r="K10">
-        <f t="shared" si="3"/>
-        <v>2.8081908830706263E-5</v>
-      </c>
-      <c r="L10">
-        <f>K10/(SUM(K$2:K$18))</f>
-        <v>0.11111111111111112</v>
-      </c>
-      <c r="M10" t="s">
-        <v>291</v>
-      </c>
-      <c r="N10" t="s">
-        <v>282</v>
       </c>
     </row>
   </sheetData>
@@ -7765,17 +7447,17 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{25E83D2B-8D51-4F58-8B18-609D52F42AB5}">
   <dimension ref="A1:U4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="11.7109375" customWidth="1"/>
-    <col min="5" max="10" width="12.5703125" customWidth="1"/>
-    <col min="11" max="11" width="15.28515625" customWidth="1"/>
-    <col min="12" max="12" width="15.140625" customWidth="1"/>
-    <col min="13" max="13" width="35.5703125" customWidth="1"/>
-    <col min="14" max="14" width="10.42578125" customWidth="1"/>
+    <col min="1" max="1" width="11.73046875" customWidth="1"/>
+    <col min="5" max="10" width="12.59765625" customWidth="1"/>
+    <col min="11" max="11" width="15.265625" customWidth="1"/>
+    <col min="12" max="12" width="15.1328125" customWidth="1"/>
+    <col min="13" max="13" width="35.59765625" customWidth="1"/>
+    <col min="14" max="14" width="10.3984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -7825,7 +7507,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:21" x14ac:dyDescent="0.45">
       <c r="A2">
         <v>4.5999999999999996</v>
       </c>
@@ -7879,7 +7561,7 @@
       <c r="T2" s="4"/>
       <c r="U2" s="5"/>
     </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:21" x14ac:dyDescent="0.45">
       <c r="A3">
         <v>4.5999999999999996</v>
       </c>
@@ -7930,7 +7612,7 @@
       <c r="T3" s="4"/>
       <c r="U3" s="5"/>
     </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:21" x14ac:dyDescent="0.45">
       <c r="A4">
         <v>4.5999999999999996</v>
       </c>
@@ -7992,13 +7674,13 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BCAE9CE0-28F2-4646-8C8D-614D783D3C78}">
   <dimension ref="A1:D37"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="15.5703125" customWidth="1"/>
-    <col min="2" max="2" width="16.42578125" customWidth="1"/>
+    <col min="1" max="1" width="15.59765625" customWidth="1"/>
+    <col min="2" max="2" width="16.3984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>261</v>
       </c>
@@ -8006,7 +7688,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A2">
         <v>1.8428292348119366E-2</v>
       </c>
@@ -8018,7 +7700,7 @@
         <v>1.8428292348119369E-2</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A3">
         <v>9.6493111884403196E-3</v>
       </c>
@@ -8030,7 +7712,7 @@
         <v>9.6493111884403213E-3</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A4">
         <v>9.7249920605065199E-3</v>
       </c>
@@ -8042,7 +7724,7 @@
         <v>9.7249920605065217E-3</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A5">
         <v>8.4737995855630632E-2</v>
       </c>
@@ -8054,7 +7736,7 @@
         <v>8.4737995855630646E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A6">
         <v>4.4369997829950332E-2</v>
       </c>
@@ -8066,7 +7748,7 @@
         <v>4.4369997829950339E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A7">
         <v>4.4717997812930337E-2</v>
       </c>
@@ -8078,7 +7760,7 @@
         <v>4.4717997812930343E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A8">
         <v>0.14057745553999376</v>
       </c>
@@ -8090,7 +7772,7 @@
         <v>0.14057745553999379</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A9">
         <v>7.3608318609236972E-2</v>
       </c>
@@ -8102,7 +7784,7 @@
         <v>7.3608318609236986E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A10">
         <v>7.4185638755191782E-2</v>
       </c>
@@ -8114,7 +7796,7 @@
         <v>7.4185638755191796E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A11">
         <v>1.8428292348119359E-2</v>
       </c>
@@ -8126,7 +7808,7 @@
         <v>1.8428292348119362E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A12">
         <v>9.6493111884403196E-3</v>
       </c>
@@ -8138,7 +7820,7 @@
         <v>9.6493111884403213E-3</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A13">
         <v>9.7249920605065199E-3</v>
       </c>
@@ -8150,7 +7832,7 @@
         <v>9.7249920605065217E-3</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A14">
         <v>8.4737995855630632E-2</v>
       </c>
@@ -8162,7 +7844,7 @@
         <v>8.4737995855630646E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A15">
         <v>4.4369997829950332E-2</v>
       </c>
@@ -8174,7 +7856,7 @@
         <v>4.4369997829950339E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A16">
         <v>4.4717997812930337E-2</v>
       </c>
@@ -8186,7 +7868,7 @@
         <v>4.4717997812930343E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A17">
         <v>0.14057745553999376</v>
       </c>
@@ -8198,7 +7880,7 @@
         <v>0.14057745553999379</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A18">
         <v>7.3608318609236972E-2</v>
       </c>
@@ -8210,7 +7892,7 @@
         <v>7.3608318609236986E-2</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A19">
         <v>7.4185638755191782E-2</v>
       </c>
@@ -8222,92 +7904,92 @@
         <v>7.4185638755191796E-2</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.45">
       <c r="B20">
         <v>5.7466262530747714E-2</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.45">
       <c r="B21">
         <v>2.3656014867026242E-2</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.45">
       <c r="B22">
         <v>3.0462698390085679E-2</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.45">
       <c r="B23">
         <v>6.5873733674516627E-2</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.45">
       <c r="B24">
         <v>2.7116954444655384E-2</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.45">
       <c r="B25">
         <v>3.4919474355617555E-2</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.45">
       <c r="B26">
         <v>5.4100037947356627E-3</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.45">
       <c r="B27">
         <v>2.2270306883183698E-3</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.45">
       <c r="B28">
         <v>2.8678272542967693E-3</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.45">
       <c r="B29">
         <v>5.7466262530747721E-2</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.45">
       <c r="B30">
         <v>2.3656014867026249E-2</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.45">
       <c r="B31">
         <v>3.0462698390085686E-2</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.45">
       <c r="B32">
         <v>6.5873733674516641E-2</v>
       </c>
     </row>
-    <row r="33" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B33">
         <v>2.7116954444655395E-2</v>
       </c>
     </row>
-    <row r="34" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B34">
         <v>3.4919474355617562E-2</v>
       </c>
     </row>
-    <row r="35" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B35">
         <v>5.4100037947356636E-3</v>
       </c>
     </row>
-    <row r="36" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B36">
         <v>2.2270306883183703E-3</v>
       </c>
     </row>
-    <row r="37" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B37">
         <v>2.8678272542967697E-3</v>
       </c>
